--- a/DataRepo/tests/data/submission_v3/multitracer_v3/study.xlsx
+++ b/DataRepo/tests/data/submission_v3/multitracer_v3/study.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-LOCAL/TRACEBASE/tracebase/DataRepo/data/tests/submission_v3/multitracer_v3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/tests/data/submission_v3/multitracer_v3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F838B44-47C2-2B43-AF0A-E362D0056905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D708D5DE-9273-3D4A-A8C0-546A1EFC5A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7280" yWindow="4920" windowWidth="39940" windowHeight="21040" tabRatio="500" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7280" yWindow="4920" windowWidth="39940" windowHeight="21040" tabRatio="500" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study" sheetId="5" r:id="rId1"/>
@@ -658,9 +658,6 @@
     <t>isocorr</t>
   </si>
   <si>
-    <t>DataRepo/data/tests/submission_v3/multitracer_v3/alaglu_cor.xlsx</t>
-  </si>
-  <si>
     <t>Sample Name</t>
   </si>
   <si>
@@ -707,6 +704,9 @@
   </si>
   <si>
     <t>Sequence</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/submission_v3/multitracer_v3/alaglu_cor.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1274,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="11" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A1" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>65</v>
@@ -1337,12 +1337,12 @@
         <v>75</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" s="14" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>76</v>
@@ -1372,22 +1372,22 @@
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>81</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>82</v>
       </c>
       <c r="K1" s="11"/>
     </row>
@@ -1399,10 +1399,10 @@
         <v>23</v>
       </c>
       <c r="C2" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="14" t="s">
         <v>83</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>84</v>
       </c>
       <c r="E2" s="19" t="s">
         <v>71</v>
@@ -1426,13 +1426,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="11" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="C1" s="21" t="s">
         <v>86</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -10632,13 +10632,13 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D1" s="11" t="s">
         <v>38</v>
@@ -10712,7 +10712,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>50</v>
